--- a/output/graficos_dimensiones/comunal_e_mediabrut_a_2022_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mediabrut_a_2022_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:28</t>
+    <t xml:space="preserve">2026-09-10 00:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mediabrut_a_2022_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mediabrut_a_2022_o higgins.xlsx
@@ -120,6 +120,9 @@
     <t xml:space="preserve">La Estrella</t>
   </si>
   <si>
+    <t xml:space="preserve">Marchigüe</t>
+  </si>
+  <si>
     <t xml:space="preserve">Navidad</t>
   </si>
   <si>
@@ -132,9 +135,6 @@
     <t xml:space="preserve">Lolol</t>
   </si>
   <si>
-    <t xml:space="preserve">Marchigüe</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:35</t>
+    <t xml:space="preserve">2026-09-18 10:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1050,13 +1050,13 @@
         <v>34</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>6205</v>
+        <v>6204</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>98.91</v>
+        <v>99.01</v>
       </c>
     </row>
     <row r="31">
@@ -1067,13 +1067,13 @@
         <v>35</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>6309</v>
+        <v>6205</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>98.84</v>
+        <v>98.91</v>
       </c>
     </row>
     <row r="32">
@@ -1084,13 +1084,13 @@
         <v>36</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>6201</v>
+        <v>6309</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>97.63</v>
+        <v>98.84</v>
       </c>
     </row>
     <row r="33">
@@ -1101,13 +1101,13 @@
         <v>37</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>6304</v>
+        <v>6201</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>96.71</v>
+        <v>97.63</v>
       </c>
     </row>
     <row r="34">
@@ -1118,10 +1118,14 @@
         <v>38</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>6204</v>
-      </c>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
+        <v>6304</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>96.71</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E34"/>
